--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/may-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/may-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7777.35</v>
+        <v>7730.74</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1502.94</v>
+        <v>1493.93</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>925.91</v>
+        <v>920.36</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1391.41</v>
+        <v>1383.08</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8709.860000000001</v>
+        <v>8657.66</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>874.41</v>
+        <v>869.17</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>911.3</v>
+        <v>905.84</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1557.7</v>
+        <v>1548.36</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>7244.38</v>
+        <v>7200.96</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1411.25</v>
+        <v>1402.79</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3652.27</v>
+        <v>3630.38</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>845.8200000000001</v>
+        <v>840.75</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1802.16</v>
+        <v>1791.36</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3691.42</v>
+        <v>3669.29</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2488.1</v>
+        <v>2473.19</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3309.22</v>
+        <v>3289.38</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>12755.83</v>
+        <v>12679.39</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>822.64</v>
+        <v>817.71</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>13564.57</v>
+        <v>13483.27</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3084.48</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2946.13</v>
+        <v>2928.48</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1010.15</v>
+        <v>1004.1</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1100.92</v>
+        <v>1094.32</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1307.21</v>
+        <v>1299.37</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>839.49</v>
+        <v>828.0700000000001</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>794.49</v>
+        <v>783.6900000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1102.72</v>
+        <v>1087.73</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>9658.93</v>
+        <v>9527.610000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1305.29</v>
+        <v>1287.54</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1107.12</v>
+        <v>1092.07</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3733.07</v>
+        <v>3682.32</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>790.12</v>
+        <v>779.38</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1195.98</v>
+        <v>1179.72</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>6994.71</v>
+        <v>6899.61</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>805.79</v>
+        <v>794.84</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1268.56</v>
+        <v>1251.32</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1928.84</v>
+        <v>1902.62</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3939.79</v>
+        <v>3886.22</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>794.14</v>
+        <v>783.34</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2517.64</v>
+        <v>2483.41</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2039.95</v>
+        <v>2012.22</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>891.47</v>
+        <v>879.35</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1228.57</v>
+        <v>1211.86</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2499.76</v>
+        <v>2465.78</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8047.32</v>
+        <v>7937.91</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8046.14</v>
+        <v>7936.75</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2104.25</v>
+        <v>2075.64</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>780.28</v>
+        <v>769.67</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1160.88</v>
+        <v>1145.09</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>928.14</v>
+        <v>915.52</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>24991.46</v>
+        <v>24778.3</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>4345.65</v>
+        <v>4308.58</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>791.25</v>
+        <v>784.51</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1652.42</v>
+        <v>1638.32</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2838.42</v>
+        <v>2814.21</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2948.63</v>
+        <v>2923.48</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2339.86</v>
+        <v>2319.91</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1445.44</v>
+        <v>1433.11</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1610.4</v>
+        <v>1596.66</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3950.59</v>
+        <v>3916.89</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1796.23</v>
+        <v>1780.91</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1223.95</v>
+        <v>1213.51</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3298.35</v>
+        <v>3270.21</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>957.34</v>
+        <v>949.1799999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>8716.17</v>
+        <v>8641.83</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1321.59</v>
+        <v>1310.32</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>874.83</v>
+        <v>867.37</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>4588.73</v>
+        <v>4549.59</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1598.13</v>
+        <v>1584.5</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1050.9</v>
+        <v>1041.94</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>10629.86</v>
+        <v>10539.19</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2606.06</v>
+        <v>2583.84</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1139.44</v>
+        <v>1129.72</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>803.89</v>
+        <v>797.04</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2147.64</v>
+        <v>2129.32</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>8323.780000000001</v>
+        <v>8252.780000000001</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2655.55</v>
+        <v>2632.9</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>792.42</v>
+        <v>785.67</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1434.01</v>
+        <v>1421.78</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>4315.82</v>
+        <v>4279.01</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>975.45</v>
+        <v>967.13</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3209.17</v>
+        <v>3181.8</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>806.22</v>
+        <v>810.5599999999999</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1030.27</v>
+        <v>1035.82</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>12907.16</v>
+        <v>12976.67</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>788.0599999999999</v>
+        <v>792.3099999999999</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>865.76</v>
+        <v>870.42</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1619.97</v>
+        <v>1628.69</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1967.27</v>
+        <v>1977.87</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3336.31</v>
+        <v>3354.28</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>942.92</v>
+        <v>948</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>6251.74</v>
+        <v>6285.41</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2740.56</v>
+        <v>2755.31</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>804.4400000000001</v>
+        <v>808.77</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2542.56</v>
+        <v>2556.25</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>974.26</v>
+        <v>979.5</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2578.68</v>
+        <v>2592.57</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1797.65</v>
+        <v>1807.33</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2280.25</v>
+        <v>2292.53</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2947.54</v>
+        <v>2963.41</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1594.42</v>
+        <v>1603.01</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1118.3</v>
+        <v>1124.32</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>998.16</v>
+        <v>1003.54</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2651.81</v>
+        <v>2666.09</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2438.64</v>
+        <v>2451.77</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1522.12</v>
+        <v>1530.31</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3404.51</v>
+        <v>3422.84</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2505.48</v>
+        <v>2518.98</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>17512.15</v>
+        <v>17606.45</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1709.24</v>
+        <v>1718.44</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>9538.09</v>
+        <v>9589.450000000001</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>792.17</v>
+        <v>796.4400000000001</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1228.45</v>
+        <v>1235.06</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2078.7</v>
+        <v>2089.89</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3271.96</v>
+        <v>3308.56</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2784.9</v>
+        <v>2816.04</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2070.33</v>
+        <v>2093.48</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1817.54</v>
+        <v>1837.86</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>24062.35</v>
+        <v>24331.46</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>20236.57</v>
+        <v>20462.89</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1099.01</v>
+        <v>1111.3</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1933.14</v>
+        <v>1954.76</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2200.66</v>
+        <v>2225.28</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2066.49</v>
+        <v>2089.6</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1871.19</v>
+        <v>1892.12</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1807.79</v>
+        <v>1828.01</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3939.88</v>
+        <v>3983.94</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1592.9</v>
+        <v>1610.72</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>5430.13</v>
+        <v>5490.86</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>5838.39</v>
+        <v>5903.68</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2219.95</v>
+        <v>2244.78</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>831.02</v>
+        <v>840.3099999999999</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>4057.95</v>
+        <v>4103.33</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1039.08</v>
+        <v>1050.71</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>4018.6</v>
+        <v>4063.54</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>15791.28</v>
+        <v>15967.89</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1270.26</v>
+        <v>1284.47</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>962.13</v>
+        <v>972.89</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>6857.15</v>
+        <v>6933.84</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>9022.43</v>
+        <v>9123.34</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>3150.45</v>
+        <v>3185.69</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1067.19</v>
+        <v>1079.12</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3637.38</v>
+        <v>3678.06</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1172.91</v>
+        <v>1186.03</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1495.36</v>
+        <v>1512.08</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>8805.309999999999</v>
+        <v>8903.790000000001</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>4455.9</v>
+        <v>4505.74</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1729.38</v>
+        <v>1748.72</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>12910.21</v>
+        <v>13054.6</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2764.62</v>
+        <v>2795.54</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>5117.37</v>
+        <v>5174.6</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>4131.42</v>
+        <v>4177.62</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2670.49</v>
+        <v>2700.36</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>3246.64</v>
+        <v>3282.95</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1417.77</v>
+        <v>1433.63</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1775.06</v>
+        <v>1794.91</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>4209.77</v>
+        <v>4256.85</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>27264.1</v>
+        <v>27569.02</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>817.14</v>
+        <v>823.33</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1855.12</v>
+        <v>1869.17</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1044.19</v>
+        <v>1052.1</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>2144.49</v>
+        <v>2160.73</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>14549.04</v>
+        <v>14659.24</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1523.61</v>
+        <v>1535.15</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1369.24</v>
+        <v>1379.61</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>875.6799999999999</v>
+        <v>882.3099999999999</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1362.95</v>
+        <v>1373.28</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>812.0700000000001</v>
+        <v>818.22</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>820.87</v>
+        <v>827.09</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1808.79</v>
+        <v>1822.49</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>5048.6</v>
+        <v>5086.84</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>8025.84</v>
+        <v>8086.63</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>811.22</v>
+        <v>817.37</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>2436.77</v>
+        <v>2455.23</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>794</v>
+        <v>800.01</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1184.89</v>
+        <v>1193.87</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>15596.51</v>
+        <v>15714.64</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>4222.27</v>
+        <v>4254.25</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1666.79</v>
+        <v>1679.42</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>9024.049999999999</v>
+        <v>9092.4</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>809.12</v>
+        <v>815.25</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1446.8</v>
+        <v>1457.76</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3557.22</v>
+        <v>3584.16</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1614.29</v>
+        <v>1626.52</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1224.83</v>
+        <v>1234.11</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>26280.64</v>
+        <v>26479.7</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1111.85</v>
+        <v>1116.06</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>953.23</v>
+        <v>956.84</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>982.95</v>
+        <v>986.6799999999999</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>866.64</v>
+        <v>869.92</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1203.43</v>
+        <v>1207.99</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1388.41</v>
+        <v>1393.67</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1865</v>
+        <v>1872.06</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>2691.17</v>
+        <v>2701.37</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2705.62</v>
+        <v>2715.87</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>926.27</v>
+        <v>929.78</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3660.1</v>
+        <v>3673.96</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>2306.46</v>
+        <v>2315.19</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>951.1900000000001</v>
+        <v>954.79</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1918.25</v>
+        <v>1925.52</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2595.33</v>
+        <v>2605.16</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>835.62</v>
+        <v>838.78</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>851.45</v>
+        <v>854.67</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1112.44</v>
+        <v>1116.65</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1278.51</v>
+        <v>1283.35</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1405.28</v>
+        <v>1410.61</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>779.8099999999999</v>
+        <v>782.76</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>20481.95</v>
+        <v>20559.55</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>3475.44</v>
+        <v>3488.61</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>10613.57</v>
+        <v>10653.78</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>916.99</v>
+        <v>920.46</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>793.0700000000001</v>
+        <v>796.08</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>1026.35</v>
+        <v>1030.24</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1548.19</v>
+        <v>1554.05</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1591.34</v>
+        <v>1597.37</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>9429.540000000001</v>
+        <v>9465.26</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>5445.44</v>
+        <v>5466.07</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>3543.43</v>
+        <v>3556.85</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>4813.07</v>
+        <v>4831.3</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>791.01</v>
+        <v>794.01</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>2585.73</v>
+        <v>2595.53</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1067.1</v>
+        <v>1071.14</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1877.46</v>
+        <v>1872.72</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>6254.75</v>
+        <v>6238.96</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>26048.9</v>
+        <v>25983.13</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1089.63</v>
+        <v>1086.88</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>4137.65</v>
+        <v>4127.21</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>31073.47</v>
+        <v>30995.02</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>793.91</v>
+        <v>791.91</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>870.42</v>
+        <v>868.22</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1592.68</v>
+        <v>1588.66</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1062.35</v>
+        <v>1059.67</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>2064.12</v>
+        <v>2058.91</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>2505.64</v>
+        <v>2499.31</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1275.97</v>
+        <v>1272.75</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>802.98</v>
+        <v>800.95</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>874.87</v>
+        <v>872.66</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1143.22</v>
+        <v>1140.33</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>835.37</v>
+        <v>833.26</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>3875.98</v>
+        <v>3866.2</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>4098.01</v>
+        <v>4087.66</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>2089.1</v>
+        <v>2083.82</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>3725.61</v>
+        <v>3716.21</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>26297.98</v>
+        <v>26231.59</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>9258.879999999999</v>
+        <v>9235.5</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>823.46</v>
+        <v>821.38</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1114</v>
+        <v>1111.18</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>843.92</v>
+        <v>841.79</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1865.26</v>
+        <v>1860.55</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1843.94</v>
+        <v>1839.29</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1394.41</v>
+        <v>1390.89</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>5940.37</v>
+        <v>5925.37</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>7755.93</v>
+        <v>7736.34</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>2707.81</v>
+        <v>2700.97</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2602.35</v>
+        <v>2595.78</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>795.04</v>
+        <v>793.03</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>3649.87</v>
+        <v>3640.66</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>4050.85</v>
+        <v>4040.62</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1179.85</v>
+        <v>1191.05</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>4714.73</v>
+        <v>4759.53</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1712.43</v>
+        <v>1728.7</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>10034.87</v>
+        <v>10130.21</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>1837.04</v>
+        <v>1854.49</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>828.01</v>
+        <v>835.87</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>35422.32</v>
+        <v>35758.86</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>811.6900000000001</v>
+        <v>819.4</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1007.76</v>
+        <v>1017.33</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>9573.67</v>
+        <v>9664.629999999999</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1135.79</v>
+        <v>1146.59</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1569.58</v>
+        <v>1584.49</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>3761.15</v>
+        <v>3796.89</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1923.41</v>
+        <v>1941.68</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1930.64</v>
+        <v>1948.99</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>3303.15</v>
+        <v>3334.53</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>948.54</v>
+        <v>957.55</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>3415.67</v>
+        <v>3448.12</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2025.24</v>
+        <v>2044.48</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>5829.64</v>
+        <v>5885.03</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>27604.79</v>
+        <v>27867.05</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>850</v>
+        <v>858.08</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>1503.83</v>
+        <v>1518.11</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1222.29</v>
+        <v>1233.9</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>793.09</v>
+        <v>800.63</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>7698.53</v>
+        <v>7771.67</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1234.15</v>
+        <v>1245.87</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>886.89</v>
+        <v>895.3200000000001</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>4404.64</v>
+        <v>4446.49</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1521.24</v>
+        <v>1535.7</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>6366.03</v>
+        <v>6426.52</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>16804.86</v>
+        <v>16964.52</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>6449.54</v>
+        <v>6510.81</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1243.03</v>
+        <v>1254.84</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>3319.49</v>
+        <v>3351.03</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>7253.22</v>
+        <v>7322.13</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1277.71</v>
+        <v>1289.85</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>1722.09</v>
+        <v>1738.45</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>2573.12</v>
+        <v>2597.56</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2394.18</v>
+        <v>2416.92</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>2124.86</v>
+        <v>2145.05</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>809.42</v>
+        <v>817.11</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>3824.38</v>
+        <v>3860.72</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>33983.34</v>
+        <v>34306.21</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1019.72</v>
+        <v>1029.4</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>30293.65</v>
+        <v>30581.46</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>896.1799999999999</v>
+        <v>902.86</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1711.82</v>
+        <v>1724.57</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>954.39</v>
+        <v>961.5</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>1172.44</v>
+        <v>1181.18</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>2161.69</v>
+        <v>2177.79</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>789.0599999999999</v>
+        <v>794.9400000000001</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>2110.03</v>
+        <v>2125.75</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>1157.18</v>
+        <v>1165.8</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>903.1799999999999</v>
+        <v>909.91</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>2503.74</v>
+        <v>2522.4</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1592.83</v>
+        <v>1604.7</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>1689.47</v>
+        <v>1702.06</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>4695.91</v>
+        <v>4730.89</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>807.35</v>
+        <v>813.37</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>3761.16</v>
+        <v>3789.18</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1045.34</v>
+        <v>1053.13</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>2911.21</v>
+        <v>2932.9</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>1305.88</v>
+        <v>1315.61</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>878.3</v>
+        <v>884.85</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>1322.25</v>
+        <v>1332.11</v>
       </c>
     </row>
     <row r="326">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>287893.54</v>
+        <v>290038.33</v>
       </c>
     </row>
     <row r="327">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>4964.95</v>
+        <v>5001.94</v>
       </c>
     </row>
     <row r="328">
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1194.35</v>
+        <v>1203.25</v>
       </c>
     </row>
     <row r="329">
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>3340.77</v>
+        <v>3365.66</v>
       </c>
     </row>
     <row r="330">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2055.35</v>
+        <v>2070.66</v>
       </c>
     </row>
     <row r="331">
@@ -20642,7 +20642,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>23353.56</v>
+        <v>23527.54</v>
       </c>
     </row>
     <row r="332">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>4039.85</v>
+        <v>4069.95</v>
       </c>
     </row>
     <row r="333">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>804.33</v>
+        <v>810.3200000000001</v>
       </c>
     </row>
     <row r="334">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>2065.25</v>
+        <v>2080.64</v>
       </c>
     </row>
     <row r="335">
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>3386.5</v>
+        <v>3411.73</v>
       </c>
     </row>
     <row r="336">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>1765.04</v>
+        <v>1778.19</v>
       </c>
     </row>
     <row r="337">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>2639.45</v>
+        <v>2659.11</v>
       </c>
     </row>
     <row r="338">
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>8134.77</v>
+        <v>8195.370000000001</v>
       </c>
     </row>
     <row r="339">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>6969.08</v>
+        <v>7021</v>
       </c>
     </row>
     <row r="340">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>6029.16</v>
+        <v>6074.08</v>
       </c>
     </row>
     <row r="341">
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>813.61</v>
+        <v>819.67</v>
       </c>
     </row>
     <row r="342">
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>1136.92</v>
+        <v>1145.39</v>
       </c>
     </row>
     <row r="343">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>2549.6</v>
+        <v>2524.18</v>
       </c>
     </row>
     <row r="344">
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>13078.18</v>
+        <v>12947.75</v>
       </c>
     </row>
     <row r="345">
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>12320.68</v>
+        <v>12197.81</v>
       </c>
     </row>
     <row r="346">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>7778.42</v>
+        <v>7700.85</v>
       </c>
     </row>
     <row r="347">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>1101.1</v>
+        <v>1090.12</v>
       </c>
     </row>
     <row r="348">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>1211.26</v>
+        <v>1199.18</v>
       </c>
     </row>
     <row r="349">
@@ -21740,7 +21740,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>3140.59</v>
+        <v>3109.27</v>
       </c>
     </row>
     <row r="350">
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>2548.53</v>
+        <v>2523.11</v>
       </c>
     </row>
     <row r="351">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>13729.92</v>
+        <v>13593</v>
       </c>
     </row>
     <row r="352">
@@ -21923,7 +21923,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>1486.93</v>
+        <v>1472.1</v>
       </c>
     </row>
     <row r="353">
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>3717.66</v>
+        <v>3680.59</v>
       </c>
     </row>
     <row r="354">
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1501.2</v>
+        <v>1486.23</v>
       </c>
     </row>
     <row r="355">
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>2614.55</v>
+        <v>2588.47</v>
       </c>
     </row>
     <row r="356">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>8803.959999999999</v>
+        <v>8716.16</v>
       </c>
     </row>
     <row r="357">
@@ -22228,7 +22228,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>934.9</v>
+        <v>925.58</v>
       </c>
     </row>
     <row r="358">
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>4455.15</v>
+        <v>4410.72</v>
       </c>
     </row>
     <row r="359">
@@ -22350,7 +22350,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>1734.68</v>
+        <v>1717.38</v>
       </c>
     </row>
     <row r="360">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>2254.73</v>
+        <v>2232.24</v>
       </c>
     </row>
     <row r="361">
@@ -22472,7 +22472,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>826.1900000000001</v>
+        <v>817.95</v>
       </c>
     </row>
     <row r="362">
@@ -22533,7 +22533,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>13060.15</v>
+        <v>12929.9</v>
       </c>
     </row>
     <row r="363">
@@ -22594,7 +22594,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>1105.53</v>
+        <v>1094.51</v>
       </c>
     </row>
     <row r="364">
@@ -22655,7 +22655,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>4594.32</v>
+        <v>4548.5</v>
       </c>
     </row>
     <row r="365">
@@ -22716,7 +22716,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>7689.07</v>
+        <v>7612.39</v>
       </c>
     </row>
     <row r="366">
@@ -22777,7 +22777,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>1165.23</v>
+        <v>1153.61</v>
       </c>
     </row>
     <row r="367">
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>1408</v>
+        <v>1393.96</v>
       </c>
     </row>
     <row r="368">
@@ -22899,7 +22899,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>799.11</v>
+        <v>791.14</v>
       </c>
     </row>
     <row r="369">
@@ -22960,7 +22960,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>17340.18</v>
+        <v>17167.25</v>
       </c>
     </row>
     <row r="370">
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>904.46</v>
+        <v>895.4400000000001</v>
       </c>
     </row>
     <row r="371">
@@ -23082,7 +23082,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>1139.14</v>
+        <v>1127.78</v>
       </c>
     </row>
     <row r="372">
@@ -23143,7 +23143,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>3278.48</v>
+        <v>3245.78</v>
       </c>
     </row>
     <row r="373">
@@ -23204,7 +23204,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>898.6900000000001</v>
+        <v>889.73</v>
       </c>
     </row>
     <row r="374">
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>1011.56</v>
+        <v>1001.48</v>
       </c>
     </row>
     <row r="375">
@@ -23326,7 +23326,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>3892.07</v>
+        <v>3853.26</v>
       </c>
     </row>
     <row r="376">
@@ -23387,7 +23387,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>2195.1</v>
+        <v>2173.21</v>
       </c>
     </row>
     <row r="377">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>2268.61</v>
+        <v>2245.98</v>
       </c>
     </row>
     <row r="378">
@@ -23509,7 +23509,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>982.86</v>
+        <v>978.55</v>
       </c>
     </row>
     <row r="379">
@@ -23570,7 +23570,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>3039.97</v>
+        <v>3026.64</v>
       </c>
     </row>
     <row r="380">
@@ -23631,7 +23631,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>2076.05</v>
+        <v>2066.95</v>
       </c>
     </row>
     <row r="381">
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>3018.5</v>
+        <v>3005.26</v>
       </c>
     </row>
     <row r="382">
@@ -23753,7 +23753,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>1048.3</v>
+        <v>1043.7</v>
       </c>
     </row>
     <row r="383">
@@ -23814,7 +23814,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>1347.04</v>
+        <v>1341.14</v>
       </c>
     </row>
     <row r="384">
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>1447.46</v>
+        <v>1441.11</v>
       </c>
     </row>
     <row r="385">
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>6756.52</v>
+        <v>6726.9</v>
       </c>
     </row>
     <row r="386">
@@ -23997,7 +23997,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>1230.73</v>
+        <v>1225.34</v>
       </c>
     </row>
     <row r="387">
@@ -24058,7 +24058,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>787.85</v>
+        <v>784.4</v>
       </c>
     </row>
     <row r="388">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>2723.99</v>
+        <v>2712.05</v>
       </c>
     </row>
     <row r="389">
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>20682.45</v>
+        <v>20591.79</v>
       </c>
     </row>
     <row r="390">
@@ -24241,7 +24241,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>1723.57</v>
+        <v>1716.02</v>
       </c>
     </row>
     <row r="391">
@@ -24302,7 +24302,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>5269.43</v>
+        <v>5246.33</v>
       </c>
     </row>
     <row r="392">
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>792.76</v>
+        <v>789.29</v>
       </c>
     </row>
     <row r="393">
@@ -24424,7 +24424,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>985.66</v>
+        <v>981.34</v>
       </c>
     </row>
     <row r="394">
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>1214.97</v>
+        <v>1209.64</v>
       </c>
     </row>
     <row r="395">
@@ -24546,7 +24546,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>1868.97</v>
+        <v>1860.78</v>
       </c>
     </row>
     <row r="396">
@@ -24607,7 +24607,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>863.46</v>
+        <v>859.6799999999999</v>
       </c>
     </row>
     <row r="397">
@@ -24668,7 +24668,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>19149.76</v>
+        <v>19065.82</v>
       </c>
     </row>
     <row r="398">
@@ -24729,7 +24729,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>1040.54</v>
+        <v>1035.98</v>
       </c>
     </row>
     <row r="399">
@@ -24790,7 +24790,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>3342.01</v>
+        <v>3327.36</v>
       </c>
     </row>
     <row r="400">
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>7349.69</v>
+        <v>7317.47</v>
       </c>
     </row>
     <row r="401">
@@ -24912,7 +24912,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>959.5599999999999</v>
+        <v>955.35</v>
       </c>
     </row>
     <row r="402">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>2705.62</v>
+        <v>2693.76</v>
       </c>
     </row>
     <row r="403">
@@ -25034,7 +25034,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>1505.65</v>
+        <v>1499.05</v>
       </c>
     </row>
     <row r="404">
@@ -25095,7 +25095,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>9578.639999999999</v>
+        <v>9536.66</v>
       </c>
     </row>
     <row r="405">
@@ -25156,7 +25156,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>3511.06</v>
+        <v>3495.67</v>
       </c>
     </row>
     <row r="406">
@@ -25217,7 +25217,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>1468.55</v>
+        <v>1462.11</v>
       </c>
     </row>
     <row r="407">
@@ -25278,7 +25278,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>15407.3</v>
+        <v>15339.77</v>
       </c>
     </row>
     <row r="408">
@@ -25339,7 +25339,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>1949.84</v>
+        <v>1941.29</v>
       </c>
     </row>
     <row r="409">
@@ -25400,7 +25400,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>3524.11</v>
+        <v>3508.66</v>
       </c>
     </row>
     <row r="410">
@@ -25461,7 +25461,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>2911.16</v>
+        <v>2898.4</v>
       </c>
     </row>
     <row r="411">
@@ -25522,7 +25522,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>998.83</v>
+        <v>994.45</v>
       </c>
     </row>
     <row r="412">
@@ -25583,7 +25583,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>786.6799999999999</v>
+        <v>783.23</v>
       </c>
     </row>
     <row r="413">
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>2953.91</v>
+        <v>2940.96</v>
       </c>
     </row>
     <row r="414">
@@ -25705,7 +25705,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>847.01</v>
+        <v>843.3</v>
       </c>
     </row>
     <row r="415">
@@ -25766,7 +25766,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>2009.56</v>
+        <v>2000.76</v>
       </c>
     </row>
     <row r="416">
@@ -25827,7 +25827,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>1443.45</v>
+        <v>1437.12</v>
       </c>
     </row>
     <row r="417">
@@ -25888,7 +25888,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>1935.35</v>
+        <v>1926.86</v>
       </c>
     </row>
     <row r="418">
@@ -25949,7 +25949,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>1039.88</v>
+        <v>1035.32</v>
       </c>
     </row>
     <row r="419">
@@ -26010,7 +26010,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>4696.85</v>
+        <v>4676.27</v>
       </c>
     </row>
     <row r="420">
@@ -26071,7 +26071,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>4375.21</v>
+        <v>4356.03</v>
       </c>
     </row>
     <row r="421">
@@ -26132,7 +26132,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>1254.31</v>
+        <v>1248.81</v>
       </c>
     </row>
     <row r="422">
@@ -26193,7 +26193,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>1186.22</v>
+        <v>1181.02</v>
       </c>
     </row>
     <row r="423">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>791.8200000000001</v>
+        <v>783.2</v>
       </c>
     </row>
     <row r="424">
@@ -26315,7 +26315,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>1271.18</v>
+        <v>1257.35</v>
       </c>
     </row>
     <row r="425">
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>2126.76</v>
+        <v>2103.62</v>
       </c>
     </row>
     <row r="426">
@@ -26437,7 +26437,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>2418.21</v>
+        <v>2391.91</v>
       </c>
     </row>
     <row r="427">
@@ -26498,7 +26498,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>2932.22</v>
+        <v>2900.32</v>
       </c>
     </row>
     <row r="428">
@@ -26559,7 +26559,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>2739.4</v>
+        <v>2709.6</v>
       </c>
     </row>
     <row r="429">
@@ -26620,7 +26620,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>1491.68</v>
+        <v>1475.45</v>
       </c>
     </row>
     <row r="430">
@@ -26681,7 +26681,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>816.79</v>
+        <v>807.91</v>
       </c>
     </row>
     <row r="431">
@@ -26742,7 +26742,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>1447.19</v>
+        <v>1431.45</v>
       </c>
     </row>
     <row r="432">
@@ -26803,7 +26803,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>1607.93</v>
+        <v>1590.44</v>
       </c>
     </row>
     <row r="433">
@@ -26864,7 +26864,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>2201.33</v>
+        <v>2177.38</v>
       </c>
     </row>
     <row r="434">
@@ -26925,7 +26925,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>793.23</v>
+        <v>784.6</v>
       </c>
     </row>
     <row r="435">
@@ -26986,7 +26986,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>5802.6</v>
+        <v>5739.47</v>
       </c>
     </row>
     <row r="436">
@@ -27047,7 +27047,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>786.52</v>
+        <v>777.96</v>
       </c>
     </row>
     <row r="437">
@@ -27108,7 +27108,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>2726.9</v>
+        <v>2697.24</v>
       </c>
     </row>
     <row r="438">
@@ -27169,7 +27169,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>4242.25</v>
+        <v>4196.1</v>
       </c>
     </row>
     <row r="439">
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>1879.74</v>
+        <v>1859.29</v>
       </c>
     </row>
     <row r="440">
@@ -27291,7 +27291,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>1727.82</v>
+        <v>1709.02</v>
       </c>
     </row>
     <row r="441">
@@ -27352,7 +27352,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>7788.1</v>
+        <v>7703.38</v>
       </c>
     </row>
     <row r="442">
@@ -27413,7 +27413,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>787.79</v>
+        <v>779.22</v>
       </c>
     </row>
     <row r="443">
@@ -27474,7 +27474,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>6824.47</v>
+        <v>6750.24</v>
       </c>
     </row>
     <row r="444">
@@ -27535,7 +27535,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>1155.29</v>
+        <v>1142.73</v>
       </c>
     </row>
     <row r="445">
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>882.98</v>
+        <v>873.37</v>
       </c>
     </row>
     <row r="446">
@@ -27657,7 +27657,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>2229.96</v>
+        <v>2205.7</v>
       </c>
     </row>
     <row r="447">
@@ -27718,7 +27718,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>4851.25</v>
+        <v>4798.47</v>
       </c>
     </row>
     <row r="448">
@@ -27779,7 +27779,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>872.61</v>
+        <v>870.63</v>
       </c>
     </row>
     <row r="449">
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>6319.61</v>
+        <v>6305.27</v>
       </c>
     </row>
     <row r="450">
@@ -27901,7 +27901,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>8801.58</v>
+        <v>8781.6</v>
       </c>
     </row>
     <row r="451">
@@ -27962,7 +27962,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>956.65</v>
+        <v>954.48</v>
       </c>
     </row>
     <row r="452">
@@ -28023,7 +28023,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>905.58</v>
+        <v>903.53</v>
       </c>
     </row>
     <row r="453">
@@ -28084,7 +28084,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>1255.25</v>
+        <v>1252.4</v>
       </c>
     </row>
     <row r="454">
@@ -28145,7 +28145,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>1113.12</v>
+        <v>1110.59</v>
       </c>
     </row>
     <row r="455">
@@ -28206,7 +28206,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>1458.26</v>
+        <v>1454.95</v>
       </c>
     </row>
     <row r="456">
@@ -28267,7 +28267,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>1542.59</v>
+        <v>1539.09</v>
       </c>
     </row>
     <row r="457">
@@ -28328,7 +28328,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>10083.46</v>
+        <v>10060.57</v>
       </c>
     </row>
     <row r="458">
@@ -28389,7 +28389,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>788.4</v>
+        <v>786.61</v>
       </c>
     </row>
     <row r="459">
@@ -28450,7 +28450,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>3812.12</v>
+        <v>3803.47</v>
       </c>
     </row>
     <row r="460">
@@ -28511,7 +28511,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>2049.5</v>
+        <v>2044.85</v>
       </c>
     </row>
     <row r="461">
@@ -28572,7 +28572,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>1122.79</v>
+        <v>1120.24</v>
       </c>
     </row>
     <row r="462">
@@ -28633,7 +28633,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>3494.61</v>
+        <v>3486.68</v>
       </c>
     </row>
     <row r="463">
@@ -28694,7 +28694,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>1063.5</v>
+        <v>1061.09</v>
       </c>
     </row>
     <row r="464">
@@ -28755,7 +28755,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>11167.37</v>
+        <v>11142.02</v>
       </c>
     </row>
     <row r="465">
@@ -28816,7 +28816,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>9461.440000000001</v>
+        <v>9439.959999999999</v>
       </c>
     </row>
     <row r="466">
@@ -28877,7 +28877,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>3756.64</v>
+        <v>3748.11</v>
       </c>
     </row>
     <row r="467">
@@ -28938,7 +28938,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>873.64</v>
+        <v>871.65</v>
       </c>
     </row>
     <row r="468">
@@ -28999,7 +28999,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>884.64</v>
+        <v>882.63</v>
       </c>
     </row>
     <row r="469">
@@ -29060,7 +29060,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>1783.07</v>
+        <v>1778.67</v>
       </c>
     </row>
     <row r="470">
@@ -29121,7 +29121,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>1113.94</v>
+        <v>1111.19</v>
       </c>
     </row>
     <row r="471">
@@ -29182,7 +29182,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>1113.45</v>
+        <v>1110.7</v>
       </c>
     </row>
     <row r="472">
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>842.38</v>
+        <v>840.3</v>
       </c>
     </row>
     <row r="473">
@@ -29304,7 +29304,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>14636.34</v>
+        <v>14600.2</v>
       </c>
     </row>
     <row r="474">
@@ -29365,7 +29365,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>1216.24</v>
+        <v>1213.24</v>
       </c>
     </row>
     <row r="475">
@@ -29426,7 +29426,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>806.28</v>
+        <v>804.29</v>
       </c>
     </row>
     <row r="476">
@@ -29487,7 +29487,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>1268.62</v>
+        <v>1265.48</v>
       </c>
     </row>
     <row r="477">
@@ -29548,7 +29548,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>2227.91</v>
+        <v>2222.41</v>
       </c>
     </row>
     <row r="478">
@@ -29609,7 +29609,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>1490.08</v>
+        <v>1486.4</v>
       </c>
     </row>
     <row r="479">
@@ -29670,7 +29670,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>2137.02</v>
+        <v>2131.74</v>
       </c>
     </row>
     <row r="480">
@@ -29731,7 +29731,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>9166.299999999999</v>
+        <v>9143.66</v>
       </c>
     </row>
     <row r="481">
@@ -29792,7 +29792,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>923.36</v>
+        <v>921.08</v>
       </c>
     </row>
     <row r="482">
@@ -29853,7 +29853,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>1332.65</v>
+        <v>1329.36</v>
       </c>
     </row>
     <row r="483">
@@ -29914,7 +29914,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>8972.190000000001</v>
+        <v>8950.030000000001</v>
       </c>
     </row>
     <row r="484">
@@ -29975,7 +29975,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>963.2</v>
+        <v>960.8200000000001</v>
       </c>
     </row>
     <row r="485">
@@ -30036,7 +30036,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>13754.99</v>
+        <v>13721.03</v>
       </c>
     </row>
     <row r="486">
@@ -30097,7 +30097,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>7590.17</v>
+        <v>7571.43</v>
       </c>
     </row>
     <row r="487">
@@ -30158,7 +30158,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>1015.33</v>
+        <v>1012.82</v>
       </c>
     </row>
     <row r="488">
@@ -30219,7 +30219,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>5288.42</v>
+        <v>5275.36</v>
       </c>
     </row>
     <row r="489">
@@ -30280,7 +30280,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>1930.6</v>
+        <v>1925.84</v>
       </c>
     </row>
     <row r="490">
@@ -30341,7 +30341,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>8420.030000000001</v>
+        <v>8399.24</v>
       </c>
     </row>
     <row r="491">
@@ -30402,7 +30402,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>3742.38</v>
+        <v>3733.14</v>
       </c>
     </row>
     <row r="492">
@@ -30463,7 +30463,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>2124.03</v>
+        <v>2118.78</v>
       </c>
     </row>
     <row r="493">
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>10014.42</v>
+        <v>9989.690000000001</v>
       </c>
     </row>
     <row r="494">
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>5121.76</v>
+        <v>5109.11</v>
       </c>
     </row>
     <row r="495">
@@ -30646,7 +30646,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>1801.5</v>
+        <v>1797.05</v>
       </c>
     </row>
     <row r="496">
@@ -30707,7 +30707,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>792.64</v>
+        <v>790.6900000000001</v>
       </c>
     </row>
     <row r="497">
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>788.85</v>
+        <v>786.9</v>
       </c>
     </row>
     <row r="498">
@@ -30829,7 +30829,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>9368.07</v>
+        <v>9344.940000000001</v>
       </c>
     </row>
     <row r="499">
@@ -30890,7 +30890,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>1863.14</v>
+        <v>1858.54</v>
       </c>
     </row>
     <row r="500">
@@ -30951,7 +30951,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>7325.48</v>
+        <v>7307.39</v>
       </c>
     </row>
     <row r="501">
@@ -31012,7 +31012,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>1107.26</v>
+        <v>1112.7</v>
       </c>
     </row>
     <row r="502">
@@ -31073,7 +31073,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>1591.06</v>
+        <v>1598.87</v>
       </c>
     </row>
     <row r="503">
@@ -31134,7 +31134,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>7333.78</v>
+        <v>7369.81</v>
       </c>
     </row>
     <row r="504">
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>1699.88</v>
+        <v>1708.23</v>
       </c>
     </row>
     <row r="505">
@@ -31256,7 +31256,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>1123.94</v>
+        <v>1129.46</v>
       </c>
     </row>
     <row r="506">
@@ -31317,7 +31317,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>7321.11</v>
+        <v>7357.07</v>
       </c>
     </row>
     <row r="507">
@@ -31378,7 +31378,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>1553.9</v>
+        <v>1561.54</v>
       </c>
     </row>
     <row r="508">
@@ -31439,7 +31439,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>1750.8</v>
+        <v>1759.4</v>
       </c>
     </row>
     <row r="509">
@@ -31500,7 +31500,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>1463.57</v>
+        <v>1470.76</v>
       </c>
     </row>
     <row r="510">
@@ -31561,7 +31561,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>1464.02</v>
+        <v>1471.21</v>
       </c>
     </row>
     <row r="511">
@@ -31622,7 +31622,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>823.5700000000001</v>
+        <v>827.62</v>
       </c>
     </row>
     <row r="512">
@@ -31683,7 +31683,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>1996.77</v>
+        <v>2006.57</v>
       </c>
     </row>
     <row r="513">
@@ -31744,7 +31744,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>4624.98</v>
+        <v>4647.69</v>
       </c>
     </row>
     <row r="514">
@@ -31805,7 +31805,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>1331.04</v>
+        <v>1337.58</v>
       </c>
     </row>
     <row r="515">
@@ -31866,7 +31866,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>2252.1</v>
+        <v>2263.16</v>
       </c>
     </row>
     <row r="516">
@@ -31927,7 +31927,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>1166.15</v>
+        <v>1171.88</v>
       </c>
     </row>
     <row r="517">
@@ -31988,7 +31988,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>2988.49</v>
+        <v>3003.17</v>
       </c>
     </row>
     <row r="518">
@@ -32049,7 +32049,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>3297.12</v>
+        <v>3313.31</v>
       </c>
     </row>
     <row r="519">
@@ -32110,7 +32110,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>801.04</v>
+        <v>804.98</v>
       </c>
     </row>
     <row r="520">
@@ -32171,7 +32171,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>4035.91</v>
+        <v>4055.73</v>
       </c>
     </row>
     <row r="521">
@@ -32232,7 +32232,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>1819.01</v>
+        <v>1827.94</v>
       </c>
     </row>
     <row r="522">
@@ -32293,7 +32293,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>1415</v>
+        <v>1421.95</v>
       </c>
     </row>
     <row r="523">
@@ -32354,7 +32354,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>804.86</v>
+        <v>808.8099999999999</v>
       </c>
     </row>
     <row r="524">
@@ -32415,7 +32415,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>1630.41</v>
+        <v>1638.42</v>
       </c>
     </row>
     <row r="525">
@@ -32476,7 +32476,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>887.9</v>
+        <v>892.26</v>
       </c>
     </row>
     <row r="526">
@@ -32537,7 +32537,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>1789.03</v>
+        <v>1797.82</v>
       </c>
     </row>
     <row r="527">
@@ -32598,7 +32598,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>874.8</v>
+        <v>879.1</v>
       </c>
     </row>
     <row r="528">
@@ -32659,7 +32659,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>4752.64</v>
+        <v>4775.99</v>
       </c>
     </row>
     <row r="529">
@@ -32720,7 +32720,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>1892.66</v>
+        <v>1901.96</v>
       </c>
     </row>
     <row r="530">
@@ -32781,7 +32781,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>1335.16</v>
+        <v>1341.72</v>
       </c>
     </row>
     <row r="531">
@@ -32842,7 +32842,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>3096.84</v>
+        <v>3112.05</v>
       </c>
     </row>
     <row r="532">
@@ -32903,7 +32903,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>813.3200000000001</v>
+        <v>816.02</v>
       </c>
     </row>
     <row r="533">
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>3939.19</v>
+        <v>3952.26</v>
       </c>
     </row>
     <row r="534">
@@ -33025,7 +33025,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>2906.6</v>
+        <v>2916.24</v>
       </c>
     </row>
     <row r="535">
@@ -33086,7 +33086,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>918.71</v>
+        <v>921.76</v>
       </c>
     </row>
     <row r="536">
@@ -33147,7 +33147,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>2425.24</v>
+        <v>2433.28</v>
       </c>
     </row>
     <row r="537">
@@ -33208,7 +33208,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>953.01</v>
+        <v>956.17</v>
       </c>
     </row>
     <row r="538">
@@ -33269,7 +33269,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>848.3200000000001</v>
+        <v>851.13</v>
       </c>
     </row>
     <row r="539">
@@ -33330,7 +33330,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>6008.86</v>
+        <v>6028.79</v>
       </c>
     </row>
     <row r="540">
@@ -33391,7 +33391,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>1637.29</v>
+        <v>1642.73</v>
       </c>
     </row>
     <row r="541">
@@ -33452,7 +33452,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>1315.51</v>
+        <v>1319.87</v>
       </c>
     </row>
     <row r="542">
@@ -33513,7 +33513,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>973.0599999999999</v>
+        <v>976.29</v>
       </c>
     </row>
     <row r="543">
@@ -33574,7 +33574,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>1406.62</v>
+        <v>1411.29</v>
       </c>
     </row>
     <row r="544">
@@ -33635,7 +33635,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>1250.71</v>
+        <v>1254.86</v>
       </c>
     </row>
     <row r="545">
@@ -33696,7 +33696,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>9445.48</v>
+        <v>9476.809999999999</v>
       </c>
     </row>
     <row r="546">
@@ -33757,7 +33757,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>3835</v>
+        <v>3847.72</v>
       </c>
     </row>
     <row r="547">
@@ -33818,7 +33818,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>4066.44</v>
+        <v>4079.93</v>
       </c>
     </row>
     <row r="548">
@@ -33879,7 +33879,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>974.39</v>
+        <v>977.62</v>
       </c>
     </row>
     <row r="549">
@@ -33940,7 +33940,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>13946.38</v>
+        <v>13992.65</v>
       </c>
     </row>
     <row r="550">
@@ -34001,7 +34001,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>3786.84</v>
+        <v>3799.4</v>
       </c>
     </row>
     <row r="551">
@@ -34062,7 +34062,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>1789.03</v>
+        <v>1794.97</v>
       </c>
     </row>
     <row r="552">
@@ -34123,7 +34123,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>803.96</v>
+        <v>806.63</v>
       </c>
     </row>
     <row r="553">
@@ -34184,7 +34184,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>3327.51</v>
+        <v>3338.55</v>
       </c>
     </row>
     <row r="554">
@@ -34245,7 +34245,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>1412.16</v>
+        <v>1416.85</v>
       </c>
     </row>
     <row r="555">
@@ -34306,7 +34306,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>2700.4</v>
+        <v>2709.36</v>
       </c>
     </row>
     <row r="556">
@@ -34367,7 +34367,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>1063.88</v>
+        <v>1067.4</v>
       </c>
     </row>
     <row r="557">
@@ -34428,7 +34428,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>857.27</v>
+        <v>860.12</v>
       </c>
     </row>
     <row r="558">
@@ -34489,7 +34489,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>4218.79</v>
+        <v>4232.78</v>
       </c>
     </row>
     <row r="559">
@@ -34550,7 +34550,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>4707.14</v>
+        <v>4722.75</v>
       </c>
     </row>
     <row r="560">
@@ -34611,7 +34611,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>3977.1</v>
+        <v>3990.3</v>
       </c>
     </row>
     <row r="561">
@@ -34672,7 +34672,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>789.85</v>
+        <v>792.47</v>
       </c>
     </row>
     <row r="562">
@@ -34733,7 +34733,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>798.74</v>
+        <v>801.39</v>
       </c>
     </row>
     <row r="563">
@@ -34794,7 +34794,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>2909.53</v>
+        <v>2919.18</v>
       </c>
     </row>
     <row r="564">
@@ -34855,7 +34855,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>2986.26</v>
+        <v>2996.17</v>
       </c>
     </row>
     <row r="565">
@@ -34916,7 +34916,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>8247.83</v>
+        <v>8275.190000000001</v>
       </c>
     </row>
     <row r="566">
@@ -34977,7 +34977,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>9923.67</v>
+        <v>9956.59</v>
       </c>
     </row>
     <row r="567">
@@ -35038,7 +35038,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>21302.73</v>
+        <v>21373.4</v>
       </c>
     </row>
     <row r="568">
@@ -35099,7 +35099,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>790.0599999999999</v>
+        <v>792.6799999999999</v>
       </c>
     </row>
     <row r="569">
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>1762.92</v>
+        <v>1768.77</v>
       </c>
     </row>
     <row r="570">
@@ -35221,7 +35221,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>6880.2</v>
+        <v>6903.02</v>
       </c>
     </row>
     <row r="571">
@@ -35282,7 +35282,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>1344.12</v>
+        <v>1348.58</v>
       </c>
     </row>
     <row r="572">
@@ -35343,7 +35343,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>17896.97</v>
+        <v>17956.34</v>
       </c>
     </row>
     <row r="573">
@@ -35404,7 +35404,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>1151.97</v>
+        <v>1155.79</v>
       </c>
     </row>
     <row r="574">
@@ -35465,7 +35465,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>876.12</v>
+        <v>879.03</v>
       </c>
     </row>
     <row r="575">
@@ -35526,7 +35526,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>1127.44</v>
+        <v>1131.18</v>
       </c>
     </row>
     <row r="576">
@@ -35587,7 +35587,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>35860.23</v>
+        <v>35979.19</v>
       </c>
     </row>
     <row r="577">
@@ -35648,7 +35648,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>9230.35</v>
+        <v>9260.969999999999</v>
       </c>
     </row>
     <row r="578">
@@ -35709,7 +35709,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>1509.24</v>
+        <v>1514.25</v>
       </c>
     </row>
     <row r="579">
@@ -35770,7 +35770,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>6467.09</v>
+        <v>6488.54</v>
       </c>
     </row>
     <row r="580">
@@ -35831,7 +35831,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>14847.86</v>
+        <v>14897.11</v>
       </c>
     </row>
     <row r="581">
@@ -35892,7 +35892,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>1064.94</v>
+        <v>1068.33</v>
       </c>
     </row>
     <row r="582">
@@ -35953,7 +35953,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>2173.99</v>
+        <v>2180.91</v>
       </c>
     </row>
     <row r="583">
@@ -36014,7 +36014,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>8201.65</v>
+        <v>8227.75</v>
       </c>
     </row>
     <row r="584">
@@ -36075,7 +36075,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>836.6</v>
+        <v>839.26</v>
       </c>
     </row>
     <row r="585">
@@ -36136,7 +36136,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>1858.1</v>
+        <v>1864.02</v>
       </c>
     </row>
     <row r="586">
@@ -36197,7 +36197,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>2031.83</v>
+        <v>2038.3</v>
       </c>
     </row>
     <row r="587">
@@ -36258,7 +36258,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>2317.9</v>
+        <v>2325.27</v>
       </c>
     </row>
     <row r="588">
@@ -36319,7 +36319,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>1382.43</v>
+        <v>1386.83</v>
       </c>
     </row>
     <row r="589">
@@ -36380,7 +36380,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>4487.01</v>
+        <v>4501.29</v>
       </c>
     </row>
     <row r="590">
@@ -36441,7 +36441,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>1043.61</v>
+        <v>1046.94</v>
       </c>
     </row>
     <row r="591">
@@ -36502,7 +36502,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>823.1799999999999</v>
+        <v>825.8</v>
       </c>
     </row>
     <row r="592">
@@ -36563,7 +36563,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>1123.89</v>
+        <v>1127.46</v>
       </c>
     </row>
     <row r="593">
@@ -36624,7 +36624,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>2785.02</v>
+        <v>2793.88</v>
       </c>
     </row>
     <row r="594">
@@ -36685,7 +36685,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>1088.8</v>
+        <v>1092.26</v>
       </c>
     </row>
     <row r="595">
@@ -36746,7 +36746,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>2024.55</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="596">
@@ -36807,7 +36807,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>840.1</v>
+        <v>842.77</v>
       </c>
     </row>
     <row r="597">
@@ -36868,7 +36868,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>7128.25</v>
+        <v>7150.94</v>
       </c>
     </row>
     <row r="598">
@@ -36929,7 +36929,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>3794</v>
+        <v>3806.07</v>
       </c>
     </row>
     <row r="599">
@@ -36990,7 +36990,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>3342.01</v>
+        <v>3352.64</v>
       </c>
     </row>
     <row r="600">
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>4804.34</v>
+        <v>4819.63</v>
       </c>
     </row>
     <row r="601">
@@ -37112,7 +37112,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>2364.72</v>
+        <v>2372.25</v>
       </c>
     </row>
     <row r="602">
@@ -37173,7 +37173,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>3412.3</v>
+        <v>3423.16</v>
       </c>
     </row>
     <row r="603">
@@ -37234,7 +37234,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>3904.09</v>
+        <v>3916.51</v>
       </c>
     </row>
     <row r="604">
@@ -37295,7 +37295,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>5029.83</v>
+        <v>5045.84</v>
       </c>
     </row>
     <row r="605">
@@ -37356,7 +37356,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>2925.23</v>
+        <v>2934.54</v>
       </c>
     </row>
     <row r="606">
@@ -37417,7 +37417,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>912.1</v>
+        <v>915</v>
       </c>
     </row>
     <row r="607">
@@ -37478,7 +37478,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>6094.64</v>
+        <v>6114.04</v>
       </c>
     </row>
     <row r="608">
@@ -37539,7 +37539,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>4512.39</v>
+        <v>4526.75</v>
       </c>
     </row>
     <row r="609">
@@ -37600,7 +37600,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>813.12</v>
+        <v>815.71</v>
       </c>
     </row>
     <row r="610">
@@ -37661,7 +37661,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>6395.47</v>
+        <v>6415.83</v>
       </c>
     </row>
     <row r="611">
@@ -37722,7 +37722,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>2081.27</v>
+        <v>2087.89</v>
       </c>
     </row>
     <row r="612">
@@ -37783,7 +37783,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>5495.39</v>
+        <v>5512.88</v>
       </c>
     </row>
     <row r="613">
@@ -37844,7 +37844,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>849.4400000000001</v>
+        <v>852.15</v>
       </c>
     </row>
     <row r="614">
@@ -37905,7 +37905,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>3898.99</v>
+        <v>3919.72</v>
       </c>
     </row>
     <row r="615">
@@ -37966,7 +37966,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>3710.64</v>
+        <v>3730.37</v>
       </c>
     </row>
     <row r="616">
@@ -38027,7 +38027,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>1046.58</v>
+        <v>1052.14</v>
       </c>
     </row>
     <row r="617">
@@ -38088,7 +38088,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>1987.23</v>
+        <v>1997.79</v>
       </c>
     </row>
     <row r="618">
@@ -38149,7 +38149,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>2226.19</v>
+        <v>2238.03</v>
       </c>
     </row>
     <row r="619">
@@ -38210,7 +38210,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>6962.71</v>
+        <v>6999.73</v>
       </c>
     </row>
     <row r="620">
@@ -38271,7 +38271,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>804.49</v>
+        <v>808.77</v>
       </c>
     </row>
     <row r="621">
@@ -38332,7 +38332,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>4460.46</v>
+        <v>4484.17</v>
       </c>
     </row>
     <row r="622">
@@ -38393,7 +38393,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>1898.35</v>
+        <v>1908.45</v>
       </c>
     </row>
     <row r="623">
@@ -38454,7 +38454,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>3830.19</v>
+        <v>3850.55</v>
       </c>
     </row>
     <row r="624">
@@ -38515,7 +38515,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>4693.29</v>
+        <v>4718.24</v>
       </c>
     </row>
     <row r="625">
@@ -38576,7 +38576,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>12108.59</v>
+        <v>12172.98</v>
       </c>
     </row>
     <row r="626">
@@ -38637,7 +38637,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>1089.4</v>
+        <v>1095.19</v>
       </c>
     </row>
     <row r="627">
@@ -38698,7 +38698,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>1740.81</v>
+        <v>1750.06</v>
       </c>
     </row>
     <row r="628">
@@ -38759,7 +38759,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>883.58</v>
+        <v>888.28</v>
       </c>
     </row>
     <row r="629">
@@ -38820,7 +38820,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>2832</v>
+        <v>2847.06</v>
       </c>
     </row>
     <row r="630">
@@ -38881,7 +38881,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>1840.82</v>
+        <v>1850.61</v>
       </c>
     </row>
     <row r="631">
@@ -38942,7 +38942,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>5804.45</v>
+        <v>5835.32</v>
       </c>
     </row>
     <row r="632">
@@ -39003,7 +39003,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>14606.39</v>
+        <v>14684.05</v>
       </c>
     </row>
     <row r="633">
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>1331.31</v>
+        <v>1338.38</v>
       </c>
     </row>
     <row r="634">
@@ -39125,7 +39125,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>2065.04</v>
+        <v>2076.02</v>
       </c>
     </row>
     <row r="635">
@@ -39186,7 +39186,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>941.95</v>
+        <v>946.96</v>
       </c>
     </row>
     <row r="636">
@@ -39247,7 +39247,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>4418.3</v>
+        <v>4441.79</v>
       </c>
     </row>
     <row r="637">
@@ -39308,7 +39308,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>963.05</v>
+        <v>968.17</v>
       </c>
     </row>
     <row r="638">
@@ -39369,7 +39369,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>838.72</v>
+        <v>843.1799999999999</v>
       </c>
     </row>
     <row r="639">
@@ -39430,7 +39430,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>1322.52</v>
+        <v>1329.55</v>
       </c>
     </row>
     <row r="640">
@@ -39491,7 +39491,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>1124.77</v>
+        <v>1130.75</v>
       </c>
     </row>
     <row r="641">
@@ -39552,7 +39552,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>4615.93</v>
+        <v>4640.47</v>
       </c>
     </row>
     <row r="642">
@@ -39613,7 +39613,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>4610.72</v>
+        <v>4635.24</v>
       </c>
     </row>
     <row r="643">
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>1135.22</v>
+        <v>1141.26</v>
       </c>
     </row>
     <row r="644">
@@ -39735,7 +39735,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>802.13</v>
+        <v>806.4</v>
       </c>
     </row>
     <row r="645">
@@ -39796,7 +39796,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>10116.23</v>
+        <v>10170.02</v>
       </c>
     </row>
     <row r="646">
@@ -39857,7 +39857,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>1749.79</v>
+        <v>1759.1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/may-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/may-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19459,7 +19459,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -20328,7 +20328,7 @@
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -21964,7 +21964,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22879,7 +22879,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -23245,7 +23245,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23367,7 +23367,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23489,7 +23489,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23550,7 +23550,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -24099,7 +24099,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24465,7 +24465,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24709,7 +24709,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24953,7 +24953,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25441,7 +25441,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25502,7 +25502,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25563,7 +25563,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -26234,7 +26234,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26661,7 +26661,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26783,7 +26783,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -27027,7 +27027,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27149,7 +27149,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -28003,7 +28003,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28552,7 +28552,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28613,7 +28613,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28796,7 +28796,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -29528,7 +29528,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29711,7 +29711,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29894,7 +29894,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29955,7 +29955,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30992,7 +30992,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31541,7 +31541,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31602,7 +31602,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31846,7 +31846,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -32212,7 +32212,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32334,7 +32334,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32456,7 +32456,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -33310,7 +33310,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33371,7 +33371,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -33737,7 +33737,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -34530,7 +34530,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34713,7 +34713,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -34957,7 +34957,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35262,7 +35262,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -36726,7 +36726,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -37092,7 +37092,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37824,7 +37824,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38373,7 +38373,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38922,7 +38922,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -38983,7 +38983,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39166,7 +39166,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/may-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/may-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1074,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1139,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1269,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1334,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1460,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1525,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1590,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1655,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1720,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1785,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1850,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1976,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2041,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2106,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2232,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2297,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2362,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2488,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2614,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2679,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2744,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2809,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2874,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2939,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3065,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3130,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3256,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3321,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3386,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3451,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3577,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3642,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3707,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3772,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3837,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3902,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3967,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4032,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4097,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4162,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4227,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4292,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4357,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4422,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4487,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4613,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4678,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4743,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4808,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4873,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4938,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5003,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5068,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5133,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5320,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5385,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5511,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5576,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5641,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5706,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5893,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5958,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6023,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6088,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6214,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6279,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6344,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6409,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6474,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6539,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6604,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6669,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6734,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6799,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6864,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6929,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6994,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7059,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7124,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7372,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7437,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7624,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7689,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7937,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8002,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8067,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8132,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8197,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8262,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8327,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8392,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8457,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8522,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8587,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8652,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8717,11 @@
           <t>77.979.117-3</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8782,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8847,11 @@
           <t>78.091.613-3</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8912,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8977,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9042,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9107,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9172,11 @@
           <t>78.085.327-1</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9298,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9363,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9428,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9493,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9558,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9623,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9688,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9753,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9879,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9944,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10009,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10074,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10139,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10204,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10330,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10395,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10460,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10586,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10651,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10716,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10781,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10846,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10911,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11037,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11102,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11167,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11232,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11297,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11362,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11427,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11492,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11618,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11744,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11809,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11874,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11939,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12004,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12069,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12134,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12321,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12386,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12451,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12516,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12581,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12646,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12711,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12776,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12841,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12906,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12971,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13036,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13101,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13166,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13231,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13296,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13361,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13487,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13552,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13617,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13682,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13747,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13812,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13877,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13942,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +14007,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14072,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14137,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14263,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14328,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14393,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14458,11 @@
           <t>77.723.304-1</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14523,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14588,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14653,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14718,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14783,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14909,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15035,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15100,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15165,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15230,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15295,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15360,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15425,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15490,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15555,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15620,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15685,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15750,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15815,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15880,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15945,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +16010,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +16075,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16140,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16205,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16331,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16396,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16461,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16526,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16591,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16656,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16721,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16847,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16912,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16977,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +17042,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17107,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17172,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17237,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17424,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17550,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17615,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17680,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17867,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17932,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17997,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +18062,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18188,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18253,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18379,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18444,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18570,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18635,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18761,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18826,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18891,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18956,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19147,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19212,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19277,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19342,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19407,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19472,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19537,11 @@
           <t>77.350.794-5</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19602,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19667,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19732,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19858,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19923,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19988,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +20053,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20118,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20244,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20309,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20374,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20439,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20504,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20569,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20634,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20699,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20764,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20829,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20894,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20959,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +21024,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +21089,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21154,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21219,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21345,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21410,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20452,7 +21540,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20513,7 +21605,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20574,7 +21670,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20635,7 +21735,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20696,7 +21800,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20818,7 +21926,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20940,7 +22052,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21001,7 +22117,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21062,7 +22182,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21123,7 +22247,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21184,7 +22312,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21306,7 +22438,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21367,7 +22503,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21428,7 +22568,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21489,7 +22633,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21550,7 +22698,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21611,7 +22763,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21672,7 +22828,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21733,7 +22893,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21794,7 +22958,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21855,7 +23023,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21916,7 +23088,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21977,7 +23153,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22038,7 +23218,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22099,7 +23283,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22282,7 +23470,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22343,7 +23535,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22465,7 +23661,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22526,7 +23726,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22709,7 +23913,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22770,7 +23978,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22892,7 +24104,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22953,7 +24169,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23014,7 +24234,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23075,7 +24299,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23258,7 +24486,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23319,7 +24551,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23380,7 +24616,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23441,7 +24681,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23502,7 +24746,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23624,7 +24872,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23685,7 +24937,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23746,7 +25002,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23807,7 +25067,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23868,7 +25132,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23929,7 +25197,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23990,7 +25262,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24051,7 +25327,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24112,7 +25392,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24173,7 +25457,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24295,7 +25583,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24356,7 +25648,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24478,7 +25774,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24661,7 +25961,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24722,7 +26026,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24783,7 +26091,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24844,7 +26156,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24905,7 +26221,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24966,7 +26286,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25027,7 +26351,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25149,7 +26477,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25210,7 +26542,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25332,7 +26668,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25393,7 +26733,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25637,7 +26981,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25698,7 +27046,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25759,7 +27111,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25820,7 +27176,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25881,7 +27241,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25942,7 +27306,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26003,7 +27371,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26125,7 +27497,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26186,7 +27562,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26369,7 +27749,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26430,7 +27814,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26491,7 +27879,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26613,7 +28005,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26674,7 +28070,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26735,7 +28135,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26857,7 +28261,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26918,7 +28326,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27040,7 +28452,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27101,7 +28517,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27162,7 +28582,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27223,7 +28647,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27284,7 +28712,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27345,7 +28777,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27467,7 +28903,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27528,7 +28968,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27650,7 +29094,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27711,7 +29159,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27772,7 +29224,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27833,7 +29289,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27894,7 +29354,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27955,7 +29419,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28016,7 +29484,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28077,7 +29549,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28138,7 +29614,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28199,7 +29679,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28260,7 +29744,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28321,7 +29809,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28382,7 +29874,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28443,7 +29939,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28565,7 +30065,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28687,7 +30191,11 @@
           <t>77.979.117-3</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28748,7 +30256,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28870,7 +30382,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28931,7 +30447,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28992,7 +30512,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29053,7 +30577,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29114,7 +30642,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29175,7 +30707,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29236,7 +30772,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29419,7 +30959,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29480,7 +31024,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29541,7 +31089,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29602,7 +31154,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29663,7 +31219,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29724,7 +31284,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29785,7 +31349,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29846,7 +31414,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29907,7 +31479,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29968,7 +31544,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30029,7 +31609,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30212,7 +31796,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30273,7 +31861,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30395,7 +31987,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30456,7 +32052,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30578,7 +32178,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30639,7 +32243,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30700,7 +32308,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30761,7 +32373,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30822,7 +32438,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30883,7 +32503,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31005,7 +32629,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31066,7 +32694,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31127,7 +32759,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31188,7 +32824,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31249,7 +32889,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31310,7 +32954,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31371,7 +33019,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31432,7 +33084,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31554,7 +33210,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31615,7 +33275,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31676,7 +33340,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31737,7 +33405,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31981,7 +33653,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32042,7 +33718,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32103,7 +33783,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32164,7 +33848,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32225,7 +33913,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32286,7 +33978,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32408,7 +34104,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32469,7 +34169,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32530,7 +34234,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32591,7 +34299,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32652,7 +34364,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32713,7 +34429,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32774,7 +34494,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32835,7 +34559,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32957,7 +34685,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33018,7 +34750,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33079,7 +34815,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33140,7 +34880,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33201,7 +34945,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33262,7 +35010,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33384,7 +35136,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33445,7 +35201,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33506,7 +35266,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33628,7 +35392,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33689,7 +35457,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33750,7 +35522,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33811,7 +35587,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33872,7 +35652,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33994,7 +35778,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34055,7 +35843,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34116,7 +35908,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34177,7 +35973,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34238,7 +36038,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34360,7 +36164,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34482,7 +36290,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34543,7 +36355,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34604,7 +36420,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34726,7 +36546,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34787,7 +36611,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34848,7 +36676,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35031,7 +36863,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35092,7 +36928,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35153,7 +36993,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35336,7 +37180,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35397,7 +37245,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35458,7 +37310,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35519,7 +37375,11 @@
           <t>77.708.749-5</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35580,7 +37440,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35641,7 +37505,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35763,7 +37631,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35824,7 +37696,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35885,7 +37761,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35946,7 +37826,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36129,7 +38013,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36190,7 +38078,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36312,7 +38204,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36373,7 +38269,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36434,7 +38334,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36495,7 +38399,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36556,7 +38464,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36617,7 +38529,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36678,7 +38594,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36739,7 +38659,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36800,7 +38724,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36861,7 +38789,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36922,7 +38854,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37044,7 +38980,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37105,7 +39045,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37166,7 +39110,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37227,7 +39175,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37288,7 +39240,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37349,7 +39305,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37410,7 +39370,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37471,7 +39435,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37532,7 +39500,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37593,7 +39565,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37654,7 +39630,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37715,7 +39695,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37776,7 +39760,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37898,7 +39886,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37959,7 +39951,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38203,7 +40199,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38264,7 +40264,11 @@
           <t>78.085.327-1</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38325,7 +40329,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38386,7 +40394,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38447,7 +40459,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38508,7 +40524,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38569,7 +40589,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38630,7 +40654,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38691,7 +40719,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38752,7 +40784,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38813,7 +40849,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38874,7 +40914,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38935,7 +40979,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38996,7 +41044,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39240,7 +41292,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39301,7 +41357,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39362,7 +41422,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39423,7 +41487,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39484,7 +41552,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39545,7 +41617,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39606,7 +41682,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39667,7 +41747,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39728,7 +41812,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39789,7 +41877,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39850,7 +41942,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
